--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7029702970297029</v>
+        <v>0.73</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6338028169014085</v>
+        <v>0.6714285714285714</v>
       </c>
       <c r="D2">
-        <v>0.4227642276422764</v>
+        <v>0.3865546218487395</v>
       </c>
       <c r="E2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
